--- a/Admininistration/Project Management Plan/topics in meetings.xlsx
+++ b/Admininistration/Project Management Plan/topics in meetings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anu365-my.sharepoint.com/personal/u5893274_anu_edu_au/Documents/Documents/sonar/Admininistration/Project Management Plan/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u5893274\OneDrive - Australian National University\Documents\sonar\Admininistration\Project Management Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="11_F25DC773A252ABDACC1048B5D9DC506E5BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6868DF77-C9BF-4FFE-870E-870E33F362FF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65F1B6C-3089-4E34-A990-EC6D97F2DF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,45 +37,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="62">
-  <si>
-    <t>Risk Category</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
   <si>
     <t>Technical</t>
   </si>
   <si>
-    <t>Security</t>
-  </si>
-  <si>
     <t>Safety</t>
   </si>
   <si>
     <t>Other</t>
   </si>
   <si>
-    <t>Hazards</t>
-  </si>
-  <si>
-    <t>Inherent Risk</t>
-  </si>
-  <si>
-    <t>Consequence</t>
-  </si>
-  <si>
-    <t>Risk rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control Measures </t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>• Implement time-division multiplexing (TDM) or frequency hopping techniques to reduce interference.
-• Ensure beacon transmissions are synchronized to avoid overlap.</t>
-  </si>
-  <si>
     <t>Almost certain</t>
   </si>
   <si>
@@ -202,31 +174,43 @@
     <t xml:space="preserve">Don’t change anything on this sheet </t>
   </si>
   <si>
-    <t>• Establish multiple communication channels e.g. email, phone, video calls.
-• Assign a team member as the main point of contact to follow up regularly.</t>
-  </si>
-  <si>
-    <t>• Assign backup members for critical tasks in advance.
-• Maintain clear documentation so another team member can take over if needed.
-• Set early deadlines to allow buffer time for unexpected absences.</t>
-  </si>
-  <si>
     <t>Use correlation based coding (Gold code)?</t>
   </si>
   <si>
-    <t>Potentially make data package shorter</t>
-  </si>
-  <si>
     <t>Try phase keying ?</t>
   </si>
   <si>
-    <t>Is delay among measurements from different beacons an issue?</t>
-  </si>
-  <si>
-    <t>equipment</t>
-  </si>
-  <si>
     <t>Where to place pool and size of pool.</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Potentially communicate to all beacons at the same time and make data package shorter</t>
+  </si>
+  <si>
+    <t>If buy large pool from overseas, shipping can take 1 month.</t>
+  </si>
+  <si>
+    <t>The power profile of the sonar is mostly lateral.</t>
+  </si>
+  <si>
+    <t>How to measure gorund truth in experiment?</t>
+  </si>
+  <si>
+    <t>Plot the sonar waveform to check if is feasible. I'm making a firmware that makes the output signal to diaphragm programable in real time and sends adc raw data back in real time.</t>
   </si>
 </sst>
 </file>
@@ -256,7 +240,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -279,30 +263,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -316,13 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -340,6 +300,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1634370</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>63184</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85DB0F6B-7EB0-93CA-3882-2F22EDAD357B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4324950" y="1317388"/>
+          <a:ext cx="1634370" cy="1560647"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -605,166 +614,118 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.6328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.36328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="74.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2">
         <v>5</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="7"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="str">
-        <f>INDEX(List!$F$2:$J$6, MATCH(C3, List!$E$2:$E$6, 0), MATCH(D3, List!$F$1:$J$1, 0))</f>
-        <v>Extreme (20)</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <f>INDEX(List!$F$2:$J$6, MATCH(C4, List!$E$2:$E$6, 0), MATCH(D4, List!$F$1:$J$1, 0))</f>
-        <v>Extreme (24)</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <f>INDEX(List!$F$2:$J$6, MATCH(C6, List!$E$2:$E$6, 0), MATCH(D6, List!$F$1:$J$1, 0))</f>
-        <v>Medium (8)</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="87" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <f>INDEX(List!$F$2:$J$6, MATCH(C7, List!$E$2:$E$6, 0), MATCH(D7, List!$F$1:$J$1, 0))</f>
-        <v>Medium (8)</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="4">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="F1:F2"/>
-  </mergeCells>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="FFFFC000"/>
+        <color rgb="FF92D050"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A00FC1BD-EF84-4D32-B60C-6CDC5C2E0D77}">
-          <x14:formula1>
-            <xm:f>List!$E$2:$E$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>C1:C1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{193EC798-DC9F-49AA-8116-829DC4705977}">
-          <x14:formula1>
-            <xm:f>List!$F$1:$J$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>D1:D1048576</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7AD89BB8-71AB-45A6-B082-FF68C50952FE}">
           <x14:formula1>
             <xm:f>List!$A$1:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>A1:A1048576</xm:sqref>
+          <xm:sqref>A1:A3 A4:A1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -787,170 +748,170 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>30</v>
+      <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>41</v>
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="4" t="s">
+    </row>
+    <row r="8" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
